--- a/작성 서류 - yun/⑤_자체평가점수표(일반)_근거기준.xlsx
+++ b/작성 서류 - yun/⑤_자체평가점수표(일반)_근거기준.xlsx
@@ -1087,7 +1087,7 @@
         <v>25</v>
       </c>
       <c r="E15" s="32" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F15" s="30">
         <f>(0.5*D15)+((0.5*D15)*(1-(E15-1)/5))</f>
@@ -1098,7 +1098,7 @@
       </c>
       <c r="M15" s="22" t="inlineStr">
         <is>
-          <t>1.3.2: 2→3등급 (01 자체평가서 판단근거 참조)</t>
+          <t>1.3.2: 2→4등급 (보관·피킹 겸용 셀 운영, 보충 자동 생성 미운영 – 01 자체평가서 판단근거 참조)</t>
         </is>
       </c>
     </row>
@@ -1711,7 +1711,7 @@
       <c r="L40" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="M40" t="inlineStr">
+      <c r="M40" s="0" t="inlineStr">
         <is>
           <t>2.1.2: 2→1등급 (주 통로 내 기둥 없음, 10개 요소 모두 적용, 2026.10.07)</t>
         </is>

--- a/작성 서류 - yun/⑤_자체평가점수표(일반)_근거기준.xlsx
+++ b/작성 서류 - yun/⑤_자체평가점수표(일반)_근거기준.xlsx
@@ -775,7 +775,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4" s="30">
         <f>(0.5*D4)+((0.5*D4)*(1-(E4-1)/5))</f>
@@ -797,7 +797,7 @@
       </c>
       <c r="M4" s="22" t="inlineStr">
         <is>
-          <t>1.1.2: 3→2등급 (공정별 인원 관리 WMS-입고 공정으로 하역 인원·작업시간 실시간 확인·분석, 2026.10.06 조정)</t>
+          <t>1.1.2: 3→2등급(10.06) → 3등급 환원 (QR 작업자 추적 시범 운영 중, 하역 인원·작업시간 실시간 관리 미정착, 2026.10.15 조정)</t>
         </is>
       </c>
     </row>

--- a/작성 서류 - yun/⑤_자체평가점수표(일반)_근거기준.xlsx
+++ b/작성 서류 - yun/⑤_자체평가점수표(일반)_근거기준.xlsx
@@ -1675,7 +1675,7 @@
         <v>20</v>
       </c>
       <c r="E39" s="32" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F39" s="30">
         <f>(0.5*D39)+((0.5*D39)*(1-(E39-1)/5))</f>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="M39" s="22" t="inlineStr">
         <is>
-          <t>2.1.1: 2→3등급 (01 자체평가서 판단근거 참조)</t>
+          <t>2.1.1: 3→2등급 (바닥 ⑧ AGV·로봇, ⑨ 자동창고 평탄도 적용 확인 → 미적용 1개, 2026.10.16 조정)</t>
         </is>
       </c>
     </row>
@@ -1729,7 +1729,7 @@
         <v>10</v>
       </c>
       <c r="E41" s="32" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F41" s="30">
         <f>(0.5*D41)+((0.5*D41)*(1-(E41-1)/5))</f>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="M41" s="22" t="inlineStr">
         <is>
-          <t>2.1.3: 2→3등급 (01 자체평가서 판단근거 참조)</t>
+          <t>2.1.3: 3→1등급 (확인 3개 모두 적용 → 미적용 0개, 2026.10.16 조정)</t>
         </is>
       </c>
     </row>
@@ -1755,19 +1755,20 @@
       <c r="D42" s="30" t="n">
         <v>20</v>
       </c>
-      <c r="E42" s="32" t="n">
-        <v>3</v>
-      </c>
-      <c r="F42" s="30">
-        <f>(0.5*D42)+((0.5*D42)*(1-(E42-1)/5))</f>
-        <v/>
+      <c r="E42" s="32" t="inlineStr">
+        <is>
+          <t>미적용</t>
+        </is>
+      </c>
+      <c r="F42" s="30" t="n">
+        <v>0</v>
       </c>
       <c r="L42" s="22" t="n">
         <v>2</v>
       </c>
       <c r="M42" s="22" t="inlineStr">
         <is>
-          <t>2.1.4: 2→3등급 (01 자체평가서 판단근거 참조)</t>
+          <t>2.1.4: 3등급→미적용 (①~④ 관리기준·조도·공기질·온습도 미적용 확인 → 미적용 6개, 0점 처리, 2026.10.16 조정)</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1785,7 @@
         <v>30</v>
       </c>
       <c r="E43" s="32" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F43" s="30">
         <f>(0.5*D43)+((0.5*D43)*(1-(E43-1)/5))</f>
@@ -1795,7 +1796,7 @@
       </c>
       <c r="M43" s="22" t="inlineStr">
         <is>
-          <t>2.1.5: 2→3등급 (01 자체평가서 판단근거 참조)</t>
+          <t>2.1.5: 3→4등급 (⑥ 랙 내진 미적용 확인 → 미적용 3개, 2026.10.16 조정)</t>
         </is>
       </c>
     </row>
